--- a/artfynd/A 22809-2024 artfynd.xlsx
+++ b/artfynd/A 22809-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119900543</v>
+        <v>119900615</v>
       </c>
       <c r="B4" t="n">
-        <v>91836</v>
+        <v>91861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,33 +911,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1009,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119900615</v>
+        <v>119900543</v>
       </c>
       <c r="B5" t="n">
-        <v>91861</v>
+        <v>91836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1017,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 22809-2024 artfynd.xlsx
+++ b/artfynd/A 22809-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119900615</v>
+        <v>119900543</v>
       </c>
       <c r="B4" t="n">
-        <v>91861</v>
+        <v>91854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1001,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119900543</v>
+        <v>119900615</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>91879</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,33 +1025,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">

--- a/artfynd/A 22809-2024 artfynd.xlsx
+++ b/artfynd/A 22809-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119900543</v>
+        <v>119900615</v>
       </c>
       <c r="B4" t="n">
-        <v>91854</v>
+        <v>91879</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,33 +911,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1009,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119900615</v>
+        <v>119900543</v>
       </c>
       <c r="B5" t="n">
-        <v>91879</v>
+        <v>91854</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1017,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
